--- a/output/pdf_financials_xlsx/BOIL.xlsx
+++ b/output/pdf_financials_xlsx/BOIL.xlsx
@@ -1079,7 +1079,7 @@
         <v>-0.08</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5396840000000001</v>
+        <v>-0.5396840000000001</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-2.463145</v>
@@ -1299,7 +1299,7 @@
         <v>-0.08</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.5396840000000001</v>
+        <v>-0.5396840000000001</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-2.463145</v>
@@ -1428,7 +1428,7 @@
         <v>-0.08</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.5396840000000001</v>
+        <v>-0.5396840000000001</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-2.463145</v>
@@ -1642,7 +1642,7 @@
         <v>-0.08</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.5396840000000001</v>
+        <v>-0.5396840000000001</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.480905</v>
@@ -1728,7 +1728,7 @@
         <v>-0.057</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.5396840000000001</v>
+        <v>-0.5396840000000001</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.187046</v>
@@ -1818,7 +1818,7 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -4579,19 +4579,19 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.902244</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>2.532</v>
       </c>
     </row>
     <row r="92">
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.36075</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -4908,7 +4908,7 @@
         <v>-0.057</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.5396840000000001</v>
+        <v>-0.5396840000000001</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-2.463145</v>
@@ -8364,7 +8364,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11728,7 +11732,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -22062,7 +22070,7 @@
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>0.5396840000000001</v>
+        <v>-0.5396840000000001</v>
       </c>
       <c r="L207" s="5" t="n">
         <v>-0.854815</v>
